--- a/paper/supplementary_data/Supplementary_Data_2_molecule_predictions.xlsx
+++ b/paper/supplementary_data/Supplementary_Data_2_molecule_predictions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="primary predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -437,10 +437,14 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="12"/>
-    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,22 +495,42 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Fixed narrow response + SMD + ConfSolv response</t>
+          <t>A_structure_only</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Fixed narrow response + SMD water</t>
+          <t>B_empirical_residual</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Fixed narrow response without SMD</t>
+          <t>C_computation_core</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Nested narrow SMD teacher selection</t>
+          <t>D_smd_water</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>E_confsolv</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F_full_solvai</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>G_narrow_reference</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>H_narrow_smd_reference</t>
         </is>
       </c>
     </row>
@@ -549,16 +573,28 @@
         <v>0.4458</v>
       </c>
       <c r="J2" t="n">
-        <v>1.168367677910053</v>
+        <v>1.229168960978835</v>
       </c>
       <c r="K2" t="n">
-        <v>1.17486164329806</v>
+        <v>1.19438755489418</v>
       </c>
       <c r="L2" t="n">
-        <v>1.164935303571429</v>
+        <v>1.190865674162257</v>
       </c>
       <c r="M2" t="n">
-        <v>1.17486164329806</v>
+        <v>1.186837386022927</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.240158454585536</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.145986098765432</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.181644240299824</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.150519895943562</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +636,28 @@
         <v>0.4947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9538592255291006</v>
+        <v>0.9140054717813033</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9447691642416217</v>
+        <v>0.9769385213844796</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9679554354056435</v>
+        <v>0.9986483919753081</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9538592255291006</v>
+        <v>0.8965290793650779</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9153365873015855</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9581741732804225</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9697001399911818</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9456077259700177</v>
       </c>
     </row>
     <row r="4">
@@ -651,16 +699,28 @@
         <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.037472090388009</v>
+        <v>1.034477460317461</v>
       </c>
       <c r="K4" t="n">
-        <v>1.03245575485009</v>
+        <v>1.063091194885363</v>
       </c>
       <c r="L4" t="n">
-        <v>1.039547173941801</v>
+        <v>1.033908147707232</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03245575485009</v>
+        <v>1.028738730158731</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.039417122134039</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.047145552910054</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.041855724867727</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.036696027336862</v>
       </c>
     </row>
     <row r="5">
@@ -702,16 +762,28 @@
         <v>0.1235</v>
       </c>
       <c r="J5" t="n">
-        <v>1.218111741181656</v>
+        <v>1.163968435846559</v>
       </c>
       <c r="K5" t="n">
-        <v>1.215775755952379</v>
+        <v>1.210280390873014</v>
       </c>
       <c r="L5" t="n">
-        <v>1.231078530423279</v>
+        <v>1.19290244951499</v>
       </c>
       <c r="M5" t="n">
-        <v>1.215775755952379</v>
+        <v>1.15411082451499</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.178159703703702</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.238038733465607</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.230297919532626</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.217681402557317</v>
       </c>
     </row>
     <row r="6">
@@ -753,16 +825,28 @@
         <v>1.3525</v>
       </c>
       <c r="J6" t="n">
-        <v>2.141073698853615</v>
+        <v>2.128369279320987</v>
       </c>
       <c r="K6" t="n">
-        <v>2.148062859347443</v>
+        <v>2.126444275573193</v>
       </c>
       <c r="L6" t="n">
-        <v>2.136603699074074</v>
+        <v>2.196515690476189</v>
       </c>
       <c r="M6" t="n">
-        <v>2.148062859347443</v>
+        <v>2.116147046296296</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.092849620811288</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.148603499559082</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.152786363977074</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.149442156525573</v>
       </c>
     </row>
     <row r="7">
@@ -804,16 +888,28 @@
         <v>1.4541</v>
       </c>
       <c r="J7" t="n">
-        <v>2.392993443562608</v>
+        <v>2.279931335978837</v>
       </c>
       <c r="K7" t="n">
-        <v>2.416423549603171</v>
+        <v>2.382517217372131</v>
       </c>
       <c r="L7" t="n">
-        <v>2.401833420194</v>
+        <v>2.418130831349204</v>
       </c>
       <c r="M7" t="n">
-        <v>2.392993443562608</v>
+        <v>2.281052044973544</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.285729610229277</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.404207093474426</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.401389865079363</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.419783545414459</v>
       </c>
     </row>
     <row r="8">
@@ -855,16 +951,28 @@
         <v>1.6352</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8546943223104062</v>
+        <v>1.268589889770722</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7572657464726634</v>
+        <v>1.170066079585537</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9384628924162254</v>
+        <v>0.1236457363315696</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7572657464726634</v>
+        <v>0.7491705923721336</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.282925052028218</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8577792535273371</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9282083064373902</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.8025833187830691</v>
       </c>
     </row>
     <row r="9">
@@ -906,16 +1014,28 @@
         <v>1.3703</v>
       </c>
       <c r="J9" t="n">
-        <v>1.854511811728395</v>
+        <v>1.828801653880071</v>
       </c>
       <c r="K9" t="n">
-        <v>1.821682294532628</v>
+        <v>1.797850706790123</v>
       </c>
       <c r="L9" t="n">
-        <v>1.79851319356261</v>
+        <v>1.449599694444443</v>
       </c>
       <c r="M9" t="n">
-        <v>1.854511811728395</v>
+        <v>1.808109552469135</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.838041467372134</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.855658334656084</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.788540086419754</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.870370116843034</v>
       </c>
     </row>
     <row r="10">
@@ -957,16 +1077,28 @@
         <v>1.3045</v>
       </c>
       <c r="J10" t="n">
-        <v>1.911881889991182</v>
+        <v>1.977806145502643</v>
       </c>
       <c r="K10" t="n">
-        <v>1.906322052469137</v>
+        <v>1.926476666887126</v>
       </c>
       <c r="L10" t="n">
-        <v>1.915536422178131</v>
+        <v>1.811470223765431</v>
       </c>
       <c r="M10" t="n">
-        <v>1.906322052469137</v>
+        <v>1.955715083774249</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.938405520502644</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.891262581349208</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.917419779320989</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.908925792989419</v>
       </c>
     </row>
     <row r="11">
@@ -1008,16 +1140,28 @@
         <v>1.3989</v>
       </c>
       <c r="J11" t="n">
-        <v>2.053033814594357</v>
+        <v>2.090479513668433</v>
       </c>
       <c r="K11" t="n">
-        <v>2.032340983906525</v>
+        <v>2.13292325</v>
       </c>
       <c r="L11" t="n">
-        <v>2.048145491181657</v>
+        <v>2.006055640211641</v>
       </c>
       <c r="M11" t="n">
-        <v>2.032340983906525</v>
+        <v>2.038720799603175</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.069972817901237</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.030073281084655</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.059332173941799</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.03034117239859</v>
       </c>
     </row>
     <row r="12">
@@ -1059,16 +1203,28 @@
         <v>1.3931</v>
       </c>
       <c r="J12" t="n">
-        <v>2.262539055114637</v>
+        <v>2.302262567460314</v>
       </c>
       <c r="K12" t="n">
-        <v>2.254919494708992</v>
+        <v>2.306245682980597</v>
       </c>
       <c r="L12" t="n">
-        <v>2.272989837301583</v>
+        <v>2.236306150352732</v>
       </c>
       <c r="M12" t="n">
-        <v>2.254919494708992</v>
+        <v>2.287912954805993</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.294266271384476</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.249311821649027</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.262130451719573</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.265595423941797</v>
       </c>
     </row>
     <row r="13">
@@ -1110,16 +1266,28 @@
         <v>1.5718</v>
       </c>
       <c r="J13" t="n">
-        <v>2.406892710537916</v>
+        <v>2.454277983686066</v>
       </c>
       <c r="K13" t="n">
-        <v>2.412845159171074</v>
+        <v>2.414278630070545</v>
       </c>
       <c r="L13" t="n">
-        <v>2.409164603174601</v>
+        <v>2.437226927028217</v>
       </c>
       <c r="M13" t="n">
-        <v>2.406892710537916</v>
+        <v>2.458076136684302</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.465017127204586</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.402834312389769</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.414972568783066</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.39448309876543</v>
       </c>
     </row>
     <row r="14">
@@ -1161,16 +1329,28 @@
         <v>1.6265</v>
       </c>
       <c r="J14" t="n">
-        <v>2.911529938271606</v>
+        <v>2.83479989638448</v>
       </c>
       <c r="K14" t="n">
-        <v>2.921600902777778</v>
+        <v>2.936314429012348</v>
       </c>
       <c r="L14" t="n">
-        <v>2.933932646604939</v>
+        <v>2.865091836419752</v>
       </c>
       <c r="M14" t="n">
-        <v>2.921600902777778</v>
+        <v>2.821922453703703</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.840469025573192</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.927295277777777</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.921293935185186</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.923588001543212</v>
       </c>
     </row>
     <row r="15">
@@ -1212,16 +1392,28 @@
         <v>0.99</v>
       </c>
       <c r="J15" t="n">
-        <v>1.264686766754849</v>
+        <v>1.10831019025573</v>
       </c>
       <c r="K15" t="n">
-        <v>1.242298335758376</v>
+        <v>1.299691006172839</v>
       </c>
       <c r="L15" t="n">
-        <v>1.211919861992944</v>
+        <v>1.180975046296295</v>
       </c>
       <c r="M15" t="n">
-        <v>1.264686766754849</v>
+        <v>0.9534639226190472</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.104707515211638</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.21669153174603</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.22140879695767</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.25277090674603</v>
       </c>
     </row>
     <row r="16">
@@ -1263,16 +1455,28 @@
         <v>0.84</v>
       </c>
       <c r="J16" t="n">
-        <v>1.226205130070549</v>
+        <v>1.199639221781307</v>
       </c>
       <c r="K16" t="n">
-        <v>1.223411529100531</v>
+        <v>1.238558173941802</v>
       </c>
       <c r="L16" t="n">
-        <v>1.229349553571431</v>
+        <v>1.18827557495591</v>
       </c>
       <c r="M16" t="n">
-        <v>1.223411529100531</v>
+        <v>1.177052207010584</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.201053849206352</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.235211453924164</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.227927535273371</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.231288699514993</v>
       </c>
     </row>
     <row r="17">
@@ -1314,16 +1518,28 @@
         <v>0.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4875438370811289</v>
+        <v>0.4994430941358028</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4849777943121694</v>
+        <v>0.4552149459876542</v>
       </c>
       <c r="L17" t="n">
-        <v>0.462125335097002</v>
+        <v>0.6477186970899482</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4875438370811289</v>
+        <v>0.4836008902116407</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.4956592561728398</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4669241578483248</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4533370414462081</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4660882374338626</v>
       </c>
     </row>
     <row r="18">
@@ -1365,16 +1581,28 @@
         <v>0.84</v>
       </c>
       <c r="J18" t="n">
-        <v>1.379694534391533</v>
+        <v>1.335489884259259</v>
       </c>
       <c r="K18" t="n">
-        <v>1.37403792217813</v>
+        <v>1.393138218694885</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38048316291887</v>
+        <v>1.389564707231041</v>
       </c>
       <c r="M18" t="n">
-        <v>1.37403792217813</v>
+        <v>1.358359120590828</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.356036281084655</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.376840496252203</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.371672845899469</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.378324596340387</v>
       </c>
     </row>
     <row r="19">
@@ -1416,16 +1644,28 @@
         <v>1.09</v>
       </c>
       <c r="J19" t="n">
-        <v>1.539764685626102</v>
+        <v>1.47315513888889</v>
       </c>
       <c r="K19" t="n">
-        <v>1.524616961199294</v>
+        <v>1.547444027777778</v>
       </c>
       <c r="L19" t="n">
-        <v>1.535520244268078</v>
+        <v>1.494954948853617</v>
       </c>
       <c r="M19" t="n">
-        <v>1.539764685626102</v>
+        <v>1.461239746913581</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.483246264991183</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.549053037037037</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.52963178968254</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.530883198412698</v>
       </c>
     </row>
     <row r="20">
@@ -1467,16 +1707,28 @@
         <v>-5.04</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.272502127425045</v>
+        <v>-4.614227193562603</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.269962059082894</v>
+        <v>-4.408513492063491</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.399835141093475</v>
+        <v>-4.567407131834215</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.269962059082894</v>
+        <v>-4.31560104717813</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-4.565750176366836</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-4.264119290123456</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-4.371586574074073</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-4.295412180335096</v>
       </c>
     </row>
     <row r="21">
@@ -1518,16 +1770,28 @@
         <v>-5.68</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.166268430335095</v>
+        <v>-4.44479831349206</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.160138348765433</v>
+        <v>-4.16988430335097</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.176074085097002</v>
+        <v>-4.229311415343914</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.166268430335095</v>
+        <v>-4.237007605820104</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-4.463055390211637</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-4.077093805114639</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-4.170238470017637</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-4.051843176807759</v>
       </c>
     </row>
     <row r="22">
@@ -1569,16 +1833,28 @@
         <v>-4.24</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.245854761904762</v>
+        <v>-3.843785780423277</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.336050425485007</v>
+        <v>-3.84789842372134</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.379960604056434</v>
+        <v>-3.402043639770719</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.245854761904762</v>
+        <v>-3.553853263668429</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-3.798993938492062</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-3.302760835537917</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-3.332547828483243</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.355645185185184</v>
       </c>
     </row>
     <row r="23">
@@ -1620,16 +1896,28 @@
         <v>-5.41</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.250904221781306</v>
+        <v>-4.313880599647262</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.246599140211642</v>
+        <v>-4.354582197971783</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.222637643298059</v>
+        <v>-4.217128593474424</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.250904221781306</v>
+        <v>-4.324071351410932</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-4.294367901234565</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-4.236144091710762</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-4.228368353174606</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-4.24405906084656</v>
       </c>
     </row>
     <row r="24">
@@ -1671,16 +1959,28 @@
         <v>-5.53</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.568036827601412</v>
+        <v>-4.533958481040557</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.59609107142857</v>
+        <v>-4.455866820987654</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.712003428130511</v>
+        <v>-4.700742250881832</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.59609107142857</v>
+        <v>-4.449475738536155</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-4.533892129629625</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-4.576524052028218</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-4.656824349647265</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-4.606893882275132</v>
       </c>
     </row>
     <row r="25">
@@ -1722,16 +2022,28 @@
         <v>-2.7798</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.957556989417989</v>
+        <v>-2.248602546296299</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.928523269400352</v>
+        <v>-2.05516522266314</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.926820826719577</v>
+        <v>-2.051332814814816</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.957556989417989</v>
+        <v>-1.926401073633158</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2.282697442680778</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.883407750000002</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.897831727072311</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.880536825396826</v>
       </c>
     </row>
     <row r="26">
@@ -1773,16 +2085,28 @@
         <v>-2.7015</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.696603130511464</v>
+        <v>-1.679843981481482</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.699654268077601</v>
+        <v>-1.521146095679013</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.684562164902998</v>
+        <v>-1.737170535714286</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.696603130511464</v>
+        <v>-1.777767526455025</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.617389093915345</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.773643540564374</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.704414861992945</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.697604422398589</v>
       </c>
     </row>
     <row r="27">
@@ -1824,16 +2148,28 @@
         <v>-5.207</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.052451973104053</v>
+        <v>-3.691709138007054</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.10282622354497</v>
+        <v>-4.482329794973542</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.263057341269838</v>
+        <v>-3.868346615961199</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.10282622354497</v>
+        <v>-3.704809071869489</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-3.73659441137566</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-4.116507749118166</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-4.295936739417988</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.026713425925926</v>
       </c>
     </row>
     <row r="28">
@@ -1875,16 +2211,28 @@
         <v>-2.3191</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.839332918871252</v>
+        <v>-2.41084740961199</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.828554448853615</v>
+        <v>-2.008417270723101</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.95605871472663</v>
+        <v>-1.716220557760139</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.828554448853615</v>
+        <v>-2.231976047178127</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-2.465286507936505</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-1.851442041446207</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.843190963403879</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.774873432539682</v>
       </c>
     </row>
     <row r="29">
@@ -1926,16 +2274,28 @@
         <v>-3.678</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.306487695767194</v>
+        <v>-3.148752402998235</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.254811530864198</v>
+        <v>-3.213732980599648</v>
       </c>
       <c r="L29" t="n">
-        <v>-3.297595623897708</v>
+        <v>-3.349767713844793</v>
       </c>
       <c r="M29" t="n">
-        <v>-3.254811530864198</v>
+        <v>-3.129992236331568</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-3.192172045855376</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-3.295875152116403</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-3.346311000881836</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-3.313368463403881</v>
       </c>
     </row>
     <row r="30">
@@ -1977,16 +2337,28 @@
         <v>-3.7325</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.271108079805997</v>
+        <v>-3.475962477954143</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.239881117724869</v>
+        <v>-3.386217008377424</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.302104464285715</v>
+        <v>-3.326019830246915</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.239881117724869</v>
+        <v>-3.388858829365078</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-3.485760185185185</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-3.292918044532629</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-3.308110526895943</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-3.298890476190477</v>
       </c>
     </row>
     <row r="31">
@@ -2028,16 +2400,28 @@
         <v>-3.7863</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.150705941358025</v>
+        <v>-3.458517096560848</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.157294356261024</v>
+        <v>-3.24855907186949</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.187373489858909</v>
+        <v>-3.283580908289242</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.157294356261024</v>
+        <v>-3.31987915564374</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-3.448268827160494</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-3.188818022486776</v>
+      </c>
+      <c r="P31" t="n">
+        <v>-3.195343694885363</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-3.199351146384481</v>
       </c>
     </row>
     <row r="32">
@@ -2079,16 +2463,28 @@
         <v>-4.1309</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.587394675925925</v>
+        <v>-3.598257550705468</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.568823963844798</v>
+        <v>-3.576475540123457</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.600347156084658</v>
+        <v>-3.555172354497357</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.587394675925925</v>
+        <v>-3.51077934303351</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-3.545766236772485</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-3.577385659171079</v>
+      </c>
+      <c r="P32" t="n">
+        <v>-3.601057991622576</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-3.596992107583773</v>
       </c>
     </row>
     <row r="33">
@@ -2130,16 +2526,28 @@
         <v>-4.1447</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.556354596560845</v>
+        <v>-3.384605412257498</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.558769433421515</v>
+        <v>-3.421342438271606</v>
       </c>
       <c r="L33" t="n">
-        <v>-3.502586022927688</v>
+        <v>-3.462021968694886</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.558769433421515</v>
+        <v>-3.695152788800703</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-3.383377788800705</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-3.538820216049382</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-3.466180346119929</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-3.536449129188711</v>
       </c>
     </row>
     <row r="34">
@@ -2181,16 +2589,28 @@
         <v>-4.1949</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.38347333553792</v>
+        <v>-3.381048170194003</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.36426479276896</v>
+        <v>-3.400777601410933</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.355297751322751</v>
+        <v>-3.299566159611993</v>
       </c>
       <c r="M34" t="n">
-        <v>-3.38347333553792</v>
+        <v>-3.372638271604939</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-3.362358432539683</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-3.367553902116402</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-3.362340255731922</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-3.375705566578481</v>
       </c>
     </row>
     <row r="35">
@@ -2232,16 +2652,28 @@
         <v>-4.2903</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.161797597001763</v>
+        <v>-3.169322211199292</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.175289274691359</v>
+        <v>-3.191858145943565</v>
       </c>
       <c r="L35" t="n">
-        <v>-3.11357997134039</v>
+        <v>-3.094876675485009</v>
       </c>
       <c r="M35" t="n">
-        <v>-3.175289274691359</v>
+        <v>-3.457682308201055</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-3.18320496031746</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-3.180741523368605</v>
+      </c>
+      <c r="P35" t="n">
+        <v>-3.117231349206349</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-3.176113458994709</v>
       </c>
     </row>
     <row r="36">
@@ -2283,16 +2715,28 @@
         <v>-3.9748</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.231247927689596</v>
+        <v>-3.086632859347441</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.272870359347444</v>
+        <v>-3.159333145943565</v>
       </c>
       <c r="L36" t="n">
-        <v>-3.237431415343916</v>
+        <v>-3.199457716049382</v>
       </c>
       <c r="M36" t="n">
-        <v>-3.272870359347444</v>
+        <v>-3.147944510582012</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-3.088568650793648</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-3.253893882275133</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-3.234668562610228</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-3.263394631834216</v>
       </c>
     </row>
     <row r="37">
@@ -2334,16 +2778,28 @@
         <v>-6.8778</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.283328097442684</v>
+        <v>-6.483702480158727</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.335991269841275</v>
+        <v>-6.403210394620807</v>
       </c>
       <c r="L37" t="n">
-        <v>-7.280967416225753</v>
+        <v>-7.789481679894183</v>
       </c>
       <c r="M37" t="n">
-        <v>-7.335991269841275</v>
+        <v>-6.41203898809523</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-6.429103395061726</v>
+      </c>
+      <c r="O37" t="n">
+        <v>-7.240937632275134</v>
+      </c>
+      <c r="P37" t="n">
+        <v>-7.225515553350976</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>-7.309470645943562</v>
       </c>
     </row>
     <row r="38">
@@ -2385,16 +2841,28 @@
         <v>-6.7004</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.531434490740736</v>
+        <v>-6.440467217813048</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.508694356261018</v>
+        <v>-6.414893474426802</v>
       </c>
       <c r="L38" t="n">
-        <v>-6.481458840388004</v>
+        <v>-6.58441758156966</v>
       </c>
       <c r="M38" t="n">
-        <v>-6.508694356261018</v>
+        <v>-6.631427744708991</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-6.48688988095238</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-6.481625507054667</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-6.42776369047619</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-6.50294625220458</v>
       </c>
     </row>
     <row r="39">
@@ -2436,16 +2904,28 @@
         <v>-6.5977</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.243475760582007</v>
+        <v>-6.242372167107585</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.238959380511457</v>
+        <v>-6.250022277336857</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.227462345679008</v>
+        <v>-6.211933057760137</v>
       </c>
       <c r="M39" t="n">
-        <v>-6.238959380511457</v>
+        <v>-6.238989473104053</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-6.24357332451499</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-6.233119609788353</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-6.239686618165778</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>-6.233058002645499</v>
       </c>
     </row>
     <row r="40">
@@ -2487,16 +2967,28 @@
         <v>-1.4551</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7441200198412702</v>
+        <v>-0.685547313712522</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.7701784964726631</v>
+        <v>-0.4908425154320988</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.7450591005291006</v>
+        <v>-0.9601905158730158</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.7701784964726631</v>
+        <v>-0.7168782319223984</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-0.6336997134038801</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.7315056569664905</v>
+      </c>
+      <c r="P40" t="n">
+        <v>-0.7125992813051146</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.7492733972663137</v>
       </c>
     </row>
     <row r="41">
@@ -2538,16 +3030,28 @@
         <v>-3.1357</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.472433156966492</v>
+        <v>-2.492899052028223</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.476542129629632</v>
+        <v>-2.478638447971783</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.474169444444446</v>
+        <v>-2.605825606261026</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.476542129629632</v>
+        <v>-2.43715679012346</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-2.506123743386247</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-2.473076884920637</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-2.483546979717814</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-2.516405881834217</v>
       </c>
     </row>
     <row r="42">
@@ -2589,16 +3093,28 @@
         <v>-4.2716</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.994736287477952</v>
+        <v>-3.890337731481481</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.974435251322751</v>
+        <v>-3.974069080687832</v>
       </c>
       <c r="L42" t="n">
-        <v>-3.954114958112875</v>
+        <v>-4.026325903880069</v>
       </c>
       <c r="M42" t="n">
-        <v>-3.974435251322751</v>
+        <v>-4.087612455908292</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-3.932272167107586</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-4.043696439594357</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-3.992643904320988</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-4.074151058201058</v>
       </c>
     </row>
     <row r="43">
@@ -2640,16 +3156,28 @@
         <v>-5.8887</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.185477612433862</v>
+        <v>-6.271254894179893</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.12121463844797</v>
+        <v>-6.159881040564369</v>
       </c>
       <c r="L43" t="n">
-        <v>-6.218039836860666</v>
+        <v>-6.233203207671956</v>
       </c>
       <c r="M43" t="n">
-        <v>-6.12121463844797</v>
+        <v>-6.35576845238095</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-6.344040873015874</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-6.253779783950615</v>
+      </c>
+      <c r="P43" t="n">
+        <v>-6.194400540123456</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>-6.155978659611993</v>
       </c>
     </row>
     <row r="44">
@@ -2691,16 +3219,28 @@
         <v>-4.9711</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.254387973985876</v>
+        <v>-5.337113029100505</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.231379045414451</v>
+        <v>-5.274719036596101</v>
       </c>
       <c r="L44" t="n">
-        <v>-5.165477072310393</v>
+        <v>-5.11424914021163</v>
       </c>
       <c r="M44" t="n">
-        <v>-5.254387973985876</v>
+        <v>-5.411601895943544</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-5.247241369047599</v>
+      </c>
+      <c r="O44" t="n">
+        <v>-5.236562147266305</v>
+      </c>
+      <c r="P44" t="n">
+        <v>-5.160004993386232</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>-5.266403791887115</v>
       </c>
     </row>
     <row r="45">
@@ -2742,16 +3282,28 @@
         <v>-4.2254</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.228963503086418</v>
+        <v>-4.21813521825397</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.236328141534391</v>
+        <v>-4.254200584215167</v>
       </c>
       <c r="L45" t="n">
-        <v>-4.205106205908288</v>
+        <v>-4.356876256613756</v>
       </c>
       <c r="M45" t="n">
-        <v>-4.236328141534391</v>
+        <v>-4.407310152116404</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-4.295347652116405</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-4.329250154320987</v>
+      </c>
+      <c r="P45" t="n">
+        <v>-4.263418441358023</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>-4.371374503968252</v>
       </c>
     </row>
     <row r="46">
@@ -2793,16 +3345,28 @@
         <v>-3.8341</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.677565685626101</v>
+        <v>-2.803655588624338</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.678525866402115</v>
+        <v>-2.687632010582008</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.680413910934744</v>
+        <v>-2.728339704585538</v>
       </c>
       <c r="M46" t="n">
-        <v>-2.678525866402115</v>
+        <v>-2.683055125661375</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-2.789575936948854</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-2.681137973985889</v>
+      </c>
+      <c r="P46" t="n">
+        <v>-2.68680104717813</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>-2.664139175485008</v>
       </c>
     </row>
     <row r="47">
@@ -2844,16 +3408,28 @@
         <v>-1.7225</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.940062775573192</v>
+        <v>-0.9051042438271604</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.9315168231922394</v>
+        <v>-0.9072992328042321</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.9365618937389771</v>
+        <v>-0.9080054607583764</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.940062775573192</v>
+        <v>-0.9082429783950617</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-0.8949103395061724</v>
+      </c>
+      <c r="O47" t="n">
+        <v>-0.9494184193121687</v>
+      </c>
+      <c r="P47" t="n">
+        <v>-0.9377102006172842</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>-0.9618975859788351</v>
       </c>
     </row>
     <row r="48">
@@ -2895,16 +3471,28 @@
         <v>-7.6381</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.040917383156963</v>
+        <v>-5.765652458112872</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.034467228835979</v>
+        <v>-6.017352733686068</v>
       </c>
       <c r="L48" t="n">
-        <v>-6.022468904320987</v>
+        <v>-6.011532705026451</v>
       </c>
       <c r="M48" t="n">
-        <v>-6.040917383156963</v>
+        <v>-5.683667107583773</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-5.84636473765432</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-6.131583190035272</v>
+      </c>
+      <c r="P48" t="n">
+        <v>-6.142979409171073</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>-6.139465421075833</v>
       </c>
     </row>
     <row r="49">
@@ -2946,16 +3534,28 @@
         <v>-7.6155</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.236754001322748</v>
+        <v>-5.900304177689605</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.228942912257492</v>
+        <v>-5.927260350529104</v>
       </c>
       <c r="L49" t="n">
-        <v>-6.2270849537037</v>
+        <v>-6.326136155202819</v>
       </c>
       <c r="M49" t="n">
-        <v>-6.236754001322748</v>
+        <v>-6.059298776455031</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-5.905331591710762</v>
+      </c>
+      <c r="O49" t="n">
+        <v>-6.315668342151672</v>
+      </c>
+      <c r="P49" t="n">
+        <v>-6.291790410052909</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>-6.303351223544972</v>
       </c>
     </row>
     <row r="50">
@@ -2997,16 +3597,28 @@
         <v>-7.6077</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.317387555114643</v>
+        <v>-6.368680610670199</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.317292934303353</v>
+        <v>-6.361344731040565</v>
       </c>
       <c r="L50" t="n">
-        <v>-6.325895789241624</v>
+        <v>-6.257829552469143</v>
       </c>
       <c r="M50" t="n">
-        <v>-6.317292934303353</v>
+        <v>-6.347405985449741</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-6.371174360670196</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-6.299778273809525</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-6.289214241622578</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>-6.316281679894185</v>
       </c>
     </row>
     <row r="51">
@@ -3048,16 +3660,28 @@
         <v>-7.1439</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.744418022486772</v>
+        <v>-5.671452689594351</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.724519775132277</v>
+        <v>-5.78096195987654</v>
       </c>
       <c r="L51" t="n">
-        <v>-5.758805809082893</v>
+        <v>-5.579002072310402</v>
       </c>
       <c r="M51" t="n">
-        <v>-5.744418022486772</v>
+        <v>-5.611140432098765</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-5.694618419312167</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-5.761756492504408</v>
+      </c>
+      <c r="P51" t="n">
+        <v>-5.747206448412697</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>-5.720340211640213</v>
       </c>
     </row>
     <row r="52">
@@ -3099,16 +3723,28 @@
         <v>-6.8106</v>
       </c>
       <c r="J52" t="n">
-        <v>-6.135898413580246</v>
+        <v>-2.286369015873014</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.171123506172841</v>
+        <v>-2.289608996472664</v>
       </c>
       <c r="L52" t="n">
-        <v>-5.419434295414463</v>
+        <v>-5.045298</v>
       </c>
       <c r="M52" t="n">
-        <v>-6.135898413580246</v>
+        <v>-4.834655164462078</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-2.529735783068781</v>
+      </c>
+      <c r="O52" t="n">
+        <v>-6.125901154761905</v>
+      </c>
+      <c r="P52" t="n">
+        <v>-5.173930033509701</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>-6.031042704144617</v>
       </c>
     </row>
     <row r="53">
@@ -3150,16 +3786,28 @@
         <v>-5.39</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.797705136684299</v>
+        <v>-4.796940674603166</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.78144106040564</v>
+        <v>-4.544055467372129</v>
       </c>
       <c r="L53" t="n">
-        <v>-4.824772982804229</v>
+        <v>-4.943155665784828</v>
       </c>
       <c r="M53" t="n">
-        <v>-4.78144106040564</v>
+        <v>-4.662279509259256</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-4.804847156084648</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-4.762084204144617</v>
+      </c>
+      <c r="P53" t="n">
+        <v>-4.807005313051142</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>-4.749002281746029</v>
       </c>
     </row>
     <row r="54">
@@ -3201,16 +3849,28 @@
         <v>-5.75</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.08627680776014</v>
+        <v>-4.980690432098772</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.148879651675483</v>
+        <v>-4.96150333994709</v>
       </c>
       <c r="L54" t="n">
-        <v>-5.125532164902999</v>
+        <v>-5.112558079805993</v>
       </c>
       <c r="M54" t="n">
-        <v>-5.08627680776014</v>
+        <v>-5.06992042548501</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-4.988654056437393</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-5.150713458994708</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-5.137673379629631</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>-5.108839252645503</v>
       </c>
     </row>
     <row r="55">
@@ -3252,16 +3912,28 @@
         <v>-5.5</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.816219025573194</v>
+        <v>-4.760840156525575</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.815711827601411</v>
+        <v>-4.805916787918872</v>
       </c>
       <c r="L55" t="n">
-        <v>-4.781863514109347</v>
+        <v>-4.792198500881832</v>
       </c>
       <c r="M55" t="n">
-        <v>-4.816219025573194</v>
+        <v>-4.812638536155202</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-4.756825352733688</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-4.8433360670194</v>
+      </c>
+      <c r="P55" t="n">
+        <v>-4.81323921957672</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>-4.83702475749559</v>
       </c>
     </row>
     <row r="56">
@@ -3303,16 +3975,28 @@
         <v>-5.88</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.920092085537916</v>
+        <v>-4.771062488977073</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.92812411816578</v>
+        <v>-5.008387334656081</v>
       </c>
       <c r="L56" t="n">
-        <v>-5.076843992504404</v>
+        <v>-5.011885582010586</v>
       </c>
       <c r="M56" t="n">
-        <v>-4.92812411816578</v>
+        <v>-4.571173611111115</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-4.762230158730158</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-4.975824404761902</v>
+      </c>
+      <c r="P56" t="n">
+        <v>-5.068015806878301</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>-4.962877998236329</v>
       </c>
     </row>
     <row r="57">
@@ -3354,16 +4038,28 @@
         <v>-5.57</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.749546130952381</v>
+        <v>-4.633585405643744</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.750935582010584</v>
+        <v>-4.735497585978836</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.674290950176367</v>
+        <v>-4.625112224426812</v>
       </c>
       <c r="M57" t="n">
-        <v>-4.750935582010584</v>
+        <v>-4.755832892416225</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-4.609405621693125</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-4.702045480599647</v>
+      </c>
+      <c r="P57" t="n">
+        <v>-4.684391302910055</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-4.712058873456789</v>
       </c>
     </row>
     <row r="58">
@@ -3405,16 +4101,28 @@
         <v>-5.99</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.528811981922399</v>
+        <v>-4.485528681657848</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.516733300264554</v>
+        <v>-4.429666380070549</v>
       </c>
       <c r="L58" t="n">
-        <v>-4.506014660493827</v>
+        <v>-4.524744257054673</v>
       </c>
       <c r="M58" t="n">
-        <v>-4.516733300264554</v>
+        <v>-4.48146634700176</v>
+      </c>
+      <c r="N58" t="n">
+        <v>-4.474255368165784</v>
+      </c>
+      <c r="O58" t="n">
+        <v>-4.529601752645505</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-4.500542779982363</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>-4.51288354276896</v>
       </c>
     </row>
     <row r="59">
@@ -3456,16 +4164,28 @@
         <v>-5.36</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.509632330246915</v>
+        <v>-4.451607837301587</v>
       </c>
       <c r="K59" t="n">
-        <v>-5.503058311287476</v>
+        <v>-4.640951741622575</v>
       </c>
       <c r="L59" t="n">
-        <v>-6.042240244708995</v>
+        <v>-5.777004265873015</v>
       </c>
       <c r="M59" t="n">
-        <v>-5.503058311287476</v>
+        <v>-4.32165954585538</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-4.480462169312168</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-5.562208245149912</v>
+      </c>
+      <c r="P59" t="n">
+        <v>-5.831837698412699</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-5.577258245149913</v>
       </c>
     </row>
     <row r="60">
@@ -3507,16 +4227,28 @@
         <v>-5.65</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.556677458112875</v>
+        <v>-4.498747486772491</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.55206354717813</v>
+        <v>-4.546255412257495</v>
       </c>
       <c r="L60" t="n">
-        <v>-4.564579001322755</v>
+        <v>-4.575225473985891</v>
       </c>
       <c r="M60" t="n">
-        <v>-4.556677458112875</v>
+        <v>-4.530260659171078</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-4.516937511022928</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-4.581373324514992</v>
+      </c>
+      <c r="P60" t="n">
+        <v>-4.571894753086419</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>-4.565655191798943</v>
       </c>
     </row>
     <row r="61">
@@ -3558,16 +4290,28 @@
         <v>-5.36</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.339035119047617</v>
+        <v>-4.31448847001763</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.341716523368605</v>
+        <v>-4.269578009259255</v>
       </c>
       <c r="L61" t="n">
-        <v>-4.382838988095237</v>
+        <v>-4.412939847883597</v>
       </c>
       <c r="M61" t="n">
-        <v>-4.341716523368605</v>
+        <v>-4.251919962522044</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-4.33402517636684</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-4.358019201940031</v>
+      </c>
+      <c r="P61" t="n">
+        <v>-4.367177050264548</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>-4.36189559082892</v>
       </c>
     </row>
     <row r="62">
@@ -3609,16 +4353,28 @@
         <v>-6.07</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.353911100088182</v>
+        <v>-4.341917361111108</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.348191997354497</v>
+        <v>-4.3125237654321</v>
       </c>
       <c r="L62" t="n">
-        <v>-4.348449294532627</v>
+        <v>-4.341608928571429</v>
       </c>
       <c r="M62" t="n">
-        <v>-4.348191997354497</v>
+        <v>-4.355546825396822</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-4.370354320987652</v>
+      </c>
+      <c r="O62" t="n">
+        <v>-4.348597288359787</v>
+      </c>
+      <c r="P62" t="n">
+        <v>-4.334633245149912</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>-4.346261397707231</v>
       </c>
     </row>
     <row r="63">
@@ -3660,16 +4416,28 @@
         <v>-5.71</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.298270370370374</v>
+        <v>-4.306010692239862</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.304065652557321</v>
+        <v>-4.350015255731924</v>
       </c>
       <c r="L63" t="n">
-        <v>-4.289573037918873</v>
+        <v>-4.29341108906526</v>
       </c>
       <c r="M63" t="n">
-        <v>-4.298270370370374</v>
+        <v>-4.336904276895946</v>
+      </c>
+      <c r="N63" t="n">
+        <v>-4.309572674162258</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-4.290406062610231</v>
+      </c>
+      <c r="P63" t="n">
+        <v>-4.301928185626106</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-4.295056536596123</v>
       </c>
     </row>
     <row r="64">
@@ -3711,16 +4479,28 @@
         <v>-6.56</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.622783697089944</v>
+        <v>-5.3813773919753</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.619901510141091</v>
+        <v>-5.585661067019394</v>
       </c>
       <c r="L64" t="n">
-        <v>-5.605552028218692</v>
+        <v>-5.475214373897699</v>
       </c>
       <c r="M64" t="n">
-        <v>-5.619901510141091</v>
+        <v>-5.461720491622571</v>
+      </c>
+      <c r="N64" t="n">
+        <v>-5.390695701058193</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-5.651143099647263</v>
+      </c>
+      <c r="P64" t="n">
+        <v>-5.610698974867721</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>-5.646653395061726</v>
       </c>
     </row>
     <row r="65">
@@ -3762,16 +4542,28 @@
         <v>-5.49</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.043847685185185</v>
+        <v>-3.893258641975297</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.066228229717811</v>
+        <v>-3.982211155202818</v>
       </c>
       <c r="L65" t="n">
-        <v>-4.017639131393294</v>
+        <v>-3.992301201499111</v>
       </c>
       <c r="M65" t="n">
-        <v>-4.043847685185185</v>
+        <v>-3.964827237654312</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-3.89183827160493</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-4.044837444885357</v>
+      </c>
+      <c r="P65" t="n">
+        <v>-3.993679508377422</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>-4.037465266754848</v>
       </c>
     </row>
     <row r="66">
@@ -3813,16 +4605,28 @@
         <v>-3.3956</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.997417372134038</v>
+        <v>-2.840726278659611</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.995244819223986</v>
+        <v>-2.972703736772488</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.954369466490299</v>
+        <v>-2.873530224867723</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.997417372134038</v>
+        <v>-2.957732561728394</v>
+      </c>
+      <c r="N66" t="n">
+        <v>-2.859552480158729</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-2.980821869488535</v>
+      </c>
+      <c r="P66" t="n">
+        <v>-2.990324548059964</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>-2.981670965608465</v>
       </c>
     </row>
     <row r="67">
@@ -3864,16 +4668,28 @@
         <v>-3.5534</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.998550859788359</v>
+        <v>-2.914604012345679</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.989636155202822</v>
+        <v>-2.99796558641975</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.967129254850089</v>
+        <v>-2.797002127425047</v>
       </c>
       <c r="M67" t="n">
-        <v>-2.989636155202822</v>
+        <v>-2.977823600088183</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-2.900037048059965</v>
+      </c>
+      <c r="O67" t="n">
+        <v>-2.942293639770723</v>
+      </c>
+      <c r="P67" t="n">
+        <v>-2.911814197530865</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>-2.950949018959437</v>
       </c>
     </row>
     <row r="68">
@@ -3915,16 +4731,28 @@
         <v>-3.5024</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.841704695767197</v>
+        <v>-2.74291080246914</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.85320806878307</v>
+        <v>-2.788420381393299</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.813195579805998</v>
+        <v>-2.867858763227515</v>
       </c>
       <c r="M68" t="n">
-        <v>-2.85320806878307</v>
+        <v>-2.822275705467375</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-2.716393827160498</v>
+      </c>
+      <c r="O68" t="n">
+        <v>-2.842810703262789</v>
+      </c>
+      <c r="P68" t="n">
+        <v>-2.808054398148149</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>-2.832011011904761</v>
       </c>
     </row>
     <row r="69">
@@ -3966,16 +4794,28 @@
         <v>-3.4002</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.596610317460319</v>
+        <v>-2.562008763227514</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.607774426807762</v>
+        <v>-2.548471263227515</v>
       </c>
       <c r="L69" t="n">
-        <v>-2.578273677248678</v>
+        <v>-2.628791854056438</v>
       </c>
       <c r="M69" t="n">
-        <v>-2.596610317460319</v>
+        <v>-2.653323798500882</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-2.560445987654322</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-2.600607517636686</v>
+      </c>
+      <c r="P69" t="n">
+        <v>-2.575622630070548</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>-2.596451741622577</v>
       </c>
     </row>
     <row r="70">
@@ -4017,16 +4857,28 @@
         <v>-10.5778</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.656464164462083</v>
+        <v>-9.795799228395056</v>
       </c>
       <c r="K70" t="n">
-        <v>-9.716404166666665</v>
+        <v>-9.784829067460317</v>
       </c>
       <c r="L70" t="n">
-        <v>-9.776180544532634</v>
+        <v>-9.768717107583774</v>
       </c>
       <c r="M70" t="n">
-        <v>-9.716404166666665</v>
+        <v>-9.588144146825398</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-9.855559898589055</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-9.672832649911813</v>
+      </c>
+      <c r="P70" t="n">
+        <v>-9.781623115079364</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-9.683307319223985</v>
       </c>
     </row>
     <row r="71">
@@ -4068,16 +4920,28 @@
         <v>-11.5197</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.909893992504408</v>
+        <v>-8.707569257054667</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.890383840388003</v>
+        <v>-9.222758741181655</v>
       </c>
       <c r="L71" t="n">
-        <v>-8.925420436507935</v>
+        <v>-8.704026113315699</v>
       </c>
       <c r="M71" t="n">
-        <v>-8.890383840388003</v>
+        <v>-8.869608212081125</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-8.723097056878304</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-8.959736474867727</v>
+      </c>
+      <c r="P71" t="n">
+        <v>-8.899260438712519</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>-8.952462996031745</v>
       </c>
     </row>
     <row r="72">
@@ -4119,16 +4983,28 @@
         <v>-9.1358</v>
       </c>
       <c r="J72" t="n">
-        <v>-7.897729949294534</v>
+        <v>-7.053119984567895</v>
       </c>
       <c r="K72" t="n">
-        <v>-7.862032308201058</v>
+        <v>-8.4605653659612</v>
       </c>
       <c r="L72" t="n">
-        <v>-7.799670370370369</v>
+        <v>-7.725279596560852</v>
       </c>
       <c r="M72" t="n">
-        <v>-7.862032308201058</v>
+        <v>-8.069731316137561</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-7.143698004850081</v>
+      </c>
+      <c r="O72" t="n">
+        <v>-7.799899503968258</v>
+      </c>
+      <c r="P72" t="n">
+        <v>-7.654561706349207</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>-7.797212312610231</v>
       </c>
     </row>
     <row r="73">
@@ -4170,16 +5046,28 @@
         <v>-10.614</v>
       </c>
       <c r="J73" t="n">
-        <v>-9.523525848765436</v>
+        <v>-9.408487962962981</v>
       </c>
       <c r="K73" t="n">
-        <v>-9.558987345679016</v>
+        <v>-9.517236397707231</v>
       </c>
       <c r="L73" t="n">
-        <v>-9.500319201940039</v>
+        <v>-9.497445337301599</v>
       </c>
       <c r="M73" t="n">
-        <v>-9.558987345679016</v>
+        <v>-9.441597696208127</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-9.385274470899487</v>
+      </c>
+      <c r="O73" t="n">
+        <v>-9.55456581790124</v>
+      </c>
+      <c r="P73" t="n">
+        <v>-9.497463921957676</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>-9.563530610670204</v>
       </c>
     </row>
     <row r="74">
@@ -4221,16 +5109,28 @@
         <v>-2.012</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.000782902116401</v>
+        <v>-1.008376113315695</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.02642752425044</v>
+        <v>-1.190602513227512</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.068225757054672</v>
+        <v>-0.9145770983245144</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.02642752425044</v>
+        <v>-0.8085556878306877</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-0.9983779905202806</v>
+      </c>
+      <c r="O74" t="n">
+        <v>-1.020135960758377</v>
+      </c>
+      <c r="P74" t="n">
+        <v>-1.08220750440917</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>-1.039088305555555</v>
       </c>
     </row>
     <row r="75">
@@ -4272,16 +5172,28 @@
         <v>-2.18</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.183087597001764</v>
+        <v>-0.9908366600529092</v>
       </c>
       <c r="K75" t="n">
-        <v>-1.215065716490299</v>
+        <v>-1.134956959876543</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.199932808641974</v>
+        <v>-1.137931259700176</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.215065716490299</v>
+        <v>-0.9561571759259264</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-0.990928858024691</v>
+      </c>
+      <c r="O75" t="n">
+        <v>-1.171267484567901</v>
+      </c>
+      <c r="P75" t="n">
+        <v>-1.216877352292769</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>-1.210916801146384</v>
       </c>
     </row>
     <row r="76">
@@ -4323,16 +5235,28 @@
         <v>-1.86</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.13282633377425</v>
+        <v>-0.9539282451499109</v>
       </c>
       <c r="K76" t="n">
-        <v>-1.142811119929453</v>
+        <v>-1.078199605379188</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.119736307319223</v>
+        <v>-1.13096343915344</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.142811119929453</v>
+        <v>-0.9588592305996478</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-0.9752451366843031</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-1.12605546957672</v>
+      </c>
+      <c r="P76" t="n">
+        <v>-1.137657579365079</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>-1.145506278659612</v>
       </c>
     </row>
     <row r="77">
@@ -4374,16 +5298,28 @@
         <v>-2.14</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.9759938844797178</v>
+        <v>-0.7796063461199304</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.907260402557319</v>
+        <v>-1.004316040564374</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.924324003527337</v>
+        <v>-0.8182208641975309</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.9759938844797178</v>
+        <v>-0.8213779744268077</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-0.7738005745149916</v>
+      </c>
+      <c r="O77" t="n">
+        <v>-0.9523405643738977</v>
+      </c>
+      <c r="P77" t="n">
+        <v>-0.942555892857143</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>-0.9449035339506168</v>
       </c>
     </row>
     <row r="78">
@@ -4425,16 +5361,28 @@
         <v>-2.13</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.500511025132274</v>
+        <v>-1.492665718694884</v>
       </c>
       <c r="K78" t="n">
-        <v>-1.481815981040563</v>
+        <v>-1.473001441798939</v>
       </c>
       <c r="L78" t="n">
-        <v>-1.516210046296295</v>
+        <v>-1.52221843121693</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.481815981040563</v>
+        <v>-1.402105599647264</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-1.427617850529098</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-1.490816360229276</v>
+      </c>
+      <c r="P78" t="n">
+        <v>-1.508761825396823</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>-1.485611177248676</v>
       </c>
     </row>
     <row r="79">
@@ -4476,16 +5424,28 @@
         <v>-2.32</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.321835255731924</v>
+        <v>-1.397291995149915</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.325136439594358</v>
+        <v>-1.425001774691361</v>
       </c>
       <c r="L79" t="n">
-        <v>-1.334557189153441</v>
+        <v>-1.301307014991184</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.321835255731924</v>
+        <v>-1.354207996031748</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-1.412178253968257</v>
+      </c>
+      <c r="O79" t="n">
+        <v>-1.335774305555557</v>
+      </c>
+      <c r="P79" t="n">
+        <v>-1.339494839065258</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>-1.327895634920636</v>
       </c>
     </row>
     <row r="80">
@@ -4527,16 +5487,28 @@
         <v>-1.97</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.406999517195768</v>
+        <v>-1.438801424162261</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.415152956349208</v>
+        <v>-1.441896578483248</v>
       </c>
       <c r="L80" t="n">
-        <v>-1.419969029982365</v>
+        <v>-1.432055670194005</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.406999517195768</v>
+        <v>-1.405482832892418</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-1.436233959435629</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-1.422149786155204</v>
+      </c>
+      <c r="P80" t="n">
+        <v>-1.406283818342153</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>-1.408816765873017</v>
       </c>
     </row>
     <row r="81">
@@ -4578,16 +5550,28 @@
         <v>-2.64</v>
       </c>
       <c r="J81" t="n">
-        <v>-1.574456307319223</v>
+        <v>-1.526454614197528</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.593292962962962</v>
+        <v>-1.660350006613756</v>
       </c>
       <c r="L81" t="n">
-        <v>-1.60581433201058</v>
+        <v>-1.572084429012344</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.574456307319223</v>
+        <v>-1.518741351410933</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-1.51895959126984</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-1.592086133156965</v>
+      </c>
+      <c r="P81" t="n">
+        <v>-1.647606380070547</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>-1.600907905643738</v>
       </c>
     </row>
     <row r="82">
@@ -4629,16 +5613,28 @@
         <v>-7.88</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.129112367724862</v>
+        <v>-6.642153703703701</v>
       </c>
       <c r="K82" t="n">
-        <v>-6.111774603174602</v>
+        <v>-6.681668474426808</v>
       </c>
       <c r="L82" t="n">
-        <v>-6.152659314373896</v>
+        <v>-6.059972552910051</v>
       </c>
       <c r="M82" t="n">
-        <v>-6.129112367724862</v>
+        <v>-6.189971626984121</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-6.544085868606698</v>
+      </c>
+      <c r="O82" t="n">
+        <v>-6.022644697971779</v>
+      </c>
+      <c r="P82" t="n">
+        <v>-6.153210251322748</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>-6.059867350088182</v>
       </c>
     </row>
     <row r="83">
@@ -4680,16 +5676,28 @@
         <v>-5.7112</v>
       </c>
       <c r="J83" t="n">
-        <v>-5.640932231040563</v>
+        <v>-5.773149415784819</v>
       </c>
       <c r="K83" t="n">
-        <v>-5.673217361111113</v>
+        <v>-5.71411215828924</v>
       </c>
       <c r="L83" t="n">
-        <v>-5.664588249559084</v>
+        <v>-5.842871704144618</v>
       </c>
       <c r="M83" t="n">
-        <v>-5.673217361111113</v>
+        <v>-5.686925936948845</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-5.688235008818331</v>
+      </c>
+      <c r="O83" t="n">
+        <v>-5.685899867724872</v>
+      </c>
+      <c r="P83" t="n">
+        <v>-5.726047464726633</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>-5.728249779541446</v>
       </c>
     </row>
     <row r="84">
@@ -4731,16 +5739,28 @@
         <v>-10.41</v>
       </c>
       <c r="J84" t="n">
-        <v>-9.755665035273376</v>
+        <v>-9.016836507936519</v>
       </c>
       <c r="K84" t="n">
-        <v>-9.813444984567909</v>
+        <v>-9.397179563492076</v>
       </c>
       <c r="L84" t="n">
-        <v>-9.731975749559091</v>
+        <v>-9.613702314814828</v>
       </c>
       <c r="M84" t="n">
-        <v>-9.813444984567909</v>
+        <v>-9.351489197530869</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-8.969656878306893</v>
+      </c>
+      <c r="O84" t="n">
+        <v>-9.74495195105821</v>
+      </c>
+      <c r="P84" t="n">
+        <v>-9.661208278218707</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>-9.698797288359794</v>
       </c>
     </row>
     <row r="85">
@@ -4782,16 +5802,28 @@
         <v>-4.72</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.819681161816576</v>
+        <v>-5.198042802028213</v>
       </c>
       <c r="K85" t="n">
-        <v>-4.869365058201057</v>
+        <v>-4.531722891093471</v>
       </c>
       <c r="L85" t="n">
-        <v>-4.782040354938268</v>
+        <v>-4.74539629717813</v>
       </c>
       <c r="M85" t="n">
-        <v>-4.819681161816576</v>
+        <v>-5.347910350529101</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-5.12800516975308</v>
+      </c>
+      <c r="O85" t="n">
+        <v>-4.854100304232805</v>
+      </c>
+      <c r="P85" t="n">
+        <v>-4.731620171957669</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>-4.877230765873015</v>
       </c>
     </row>
     <row r="86">
@@ -4833,16 +5865,28 @@
         <v>-5.5293</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.60747799823633</v>
+        <v>-4.030718397266313</v>
       </c>
       <c r="K86" t="n">
-        <v>-4.562793871252201</v>
+        <v>-4.26331879409171</v>
       </c>
       <c r="L86" t="n">
-        <v>-4.562205092592594</v>
+        <v>-4.510078824955909</v>
       </c>
       <c r="M86" t="n">
-        <v>-4.60747799823633</v>
+        <v>-4.0117319664903</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-4.003697332451497</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-4.565645866402115</v>
+      </c>
+      <c r="P86" t="n">
+        <v>-4.614008333333331</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>-4.577659248236333</v>
       </c>
     </row>
   </sheetData>
